--- a/Mantenimiento/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,7 +1302,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA_MOLINA</t>
+          <t>LA MOLINA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1420,10 +1330,52 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>150114</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LA MOLINA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>307670</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VIRGEN DEL ROSARIO DE YUNGAY</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>-12.06875</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-76.94147</v>
+      </c>
+      <c r="I20" t="n">
+        <v>138</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-LA_MOLINA.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-LA_MOLINA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>ATENEO DE LA MOLINA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.10812</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.93940000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>324</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.10812</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.9394</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>1286 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.11708</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.93774999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>641</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.11708</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.93775</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>1230 SULPICIO GARCIA PEÑALOZA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.09547</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.94153</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1294</v>
-      </c>
-      <c r="J4" t="n">
-        <v>60</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.09547</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.94153</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>1235 UNION LATINOAMERICANA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.06467</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.9426</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1728</v>
-      </c>
-      <c r="J5" t="n">
-        <v>69</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.06467</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.9426</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>136</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.06634</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.94078</v>
-      </c>
-      <c r="I6" t="n">
-        <v>487</v>
-      </c>
-      <c r="J6" t="n">
-        <v>26</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.06634</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.94078</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>0028 JESUS Y MARIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.07615</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.97365000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>455</v>
-      </c>
-      <c r="J7" t="n">
-        <v>28</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.07615</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.97365</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>1278 MIXTO LA MOLINA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.0704</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.94457</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2502</v>
-      </c>
-      <c r="J8" t="n">
-        <v>73</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.0704</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.94457</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>ING. CARLOS LISSON BEINGOLEA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.06741</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.95108</v>
-      </c>
-      <c r="I9" t="n">
-        <v>432</v>
-      </c>
-      <c r="J9" t="n">
-        <v>69</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.06741</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.95108</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>JEAN LE BOULCH</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.06473</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.94944</v>
-      </c>
-      <c r="I10" t="n">
-        <v>405</v>
-      </c>
-      <c r="J10" t="n">
-        <v>27</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.06473</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.94944</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>MAYOR PIP FELIX ROMAN TELLO ROJAS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.07066</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.93974</v>
-      </c>
-      <c r="I11" t="n">
-        <v>876</v>
-      </c>
-      <c r="J11" t="n">
-        <v>44</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.07066</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.93974</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>SAGRADO CORAZON DE LA MOLINA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.06417</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.95887999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>387</v>
-      </c>
-      <c r="J12" t="n">
-        <v>31</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.06417</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.95888</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>ALTAIR</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.0934</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.95053</v>
-      </c>
-      <c r="I13" t="n">
-        <v>675</v>
-      </c>
-      <c r="J13" t="n">
-        <v>78</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.0934</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.95053</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>LORD BYRON</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.08319</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.90755</v>
-      </c>
-      <c r="I14" t="n">
-        <v>651</v>
-      </c>
-      <c r="J14" t="n">
-        <v>48</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.08319</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.90755</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>HORMIGUITAS DE NEWMAN / JUAN ENRIQUE NEWMAN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.10236</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.94687999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>453</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.10236</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.94688</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>SANTA FELICIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.06312</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.95501</v>
-      </c>
-      <c r="I16" t="n">
-        <v>261</v>
-      </c>
-      <c r="J16" t="n">
-        <v>37</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.06312</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.95501</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.10444</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.94204000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>219</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.10444</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.94204</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>NEW JEAN PIAGET COLLEGE</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.11677</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.93397</v>
-      </c>
-      <c r="I18" t="n">
-        <v>142</v>
-      </c>
-      <c r="J18" t="n">
-        <v>24</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.11677</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.93397</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>SHALOOM</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.08845</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.88668</v>
-      </c>
-      <c r="I19" t="n">
-        <v>243</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.08845</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.88668</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>VIRGEN DEL ROSARIO DE YUNGAY</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.06875</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.94147</v>
-      </c>
-      <c r="I20" t="n">
-        <v>138</v>
-      </c>
-      <c r="J20" t="n">
-        <v>11</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.06875</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.94147</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
